--- a/Day 1_Manual Testing/Ankan_Nayak_MagicBricks_Group4.xlsx
+++ b/Day 1_Manual Testing/Ankan_Nayak_MagicBricks_Group4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ankan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{37413790-388F-4A26-8D6B-96558A6FCDE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DF4D5769-9F8A-4BE4-BFDB-25CE9736E131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="User story" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="425">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -1319,6 +1319,53 @@
   </si>
   <si>
     <t>User has contacted an owner/agent for at least one property, user currnetly on "Shortlisted" tab</t>
+  </si>
+  <si>
+    <t>Share Feedback</t>
+  </si>
+  <si>
+    <t>1. Navigate to Contacted tab
+2. Observe listed properties                                                              3. click on a propert                                                                              4. Click Share feedback and share it</t>
+  </si>
+  <si>
+    <t>Only properties for which the user initiated contact are shown and User can give Feedback</t>
+  </si>
+  <si>
+    <t>TS_Rent_17</t>
+  </si>
+  <si>
+    <t>REQ_Rent_17</t>
+  </si>
+  <si>
+    <t>Verify user can view contacted and share feedback</t>
+  </si>
+  <si>
+    <t>1. To validate Feedback is possible</t>
+  </si>
+  <si>
+    <t>Location Details</t>
+  </si>
+  <si>
+    <t>To validate user can view all location details</t>
+  </si>
+  <si>
+    <t>1. Click on any listing card
+2. Observe the property detail page                                                    3. Click on location</t>
+  </si>
+  <si>
+    <t>Full location details are displayed: photos, rent, description, closest routes etc</t>
+  </si>
+  <si>
+    <t>TS_Rent_18</t>
+  </si>
+  <si>
+    <t>REQ_Rent_18</t>
+  </si>
+  <si>
+    <t>Verify user can view locations details</t>
+  </si>
+  <si>
+    <t>1. To validate location shows location details</t>
   </si>
 </sst>
 </file>
@@ -1328,7 +1375,7 @@
   <numFmts count="1">
     <numFmt numFmtId="6" formatCode="&quot;₹&quot;\ #,##0;[Red]&quot;₹&quot;\ \-#,##0"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1442,8 +1489,15 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1580,8 +1634,20 @@
         <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1680,11 +1746,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1816,6 +1893,21 @@
     <xf numFmtId="0" fontId="15" fillId="26" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="14" fillId="24" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="22" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1834,20 +1926,42 @@
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="6" fontId="14" fillId="24" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1857,8 +1971,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFFFCC"/>
       <color rgb="FFCCFFCC"/>
-      <color rgb="FFFFFFCC"/>
       <color rgb="FFFFCC99"/>
       <color rgb="FFFFFF99"/>
     </mruColors>
@@ -2505,7 +2619,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="20" customWidth="1"/>
@@ -2536,14 +2650,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="49" t="s">
+      <c r="A2" s="54" t="s">
         <v>284</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="51"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="56"/>
     </row>
     <row r="3" spans="1:6" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
@@ -2586,14 +2700,14 @@
       </c>
     </row>
     <row r="5" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="54" t="s">
         <v>292</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="51"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="56"/>
     </row>
     <row r="6" spans="1:6" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="30" t="s">
@@ -2616,14 +2730,14 @@
       </c>
     </row>
     <row r="7" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="52" t="s">
+      <c r="A7" s="57" t="s">
         <v>296</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="51"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55"/>
+      <c r="F7" s="56"/>
     </row>
     <row r="8" spans="1:6" ht="29.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="35" t="s">
@@ -2666,14 +2780,14 @@
       </c>
     </row>
     <row r="10" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="49" t="s">
+      <c r="A10" s="54" t="s">
         <v>303</v>
       </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="51"/>
+      <c r="B10" s="55"/>
+      <c r="C10" s="55"/>
+      <c r="D10" s="55"/>
+      <c r="E10" s="55"/>
+      <c r="F10" s="56"/>
     </row>
     <row r="11" spans="1:6" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="35" t="s">
@@ -2696,14 +2810,14 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="57" t="s">
         <v>307</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="51"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="56"/>
     </row>
     <row r="13" spans="1:6" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="35" t="s">
@@ -2726,14 +2840,14 @@
       </c>
     </row>
     <row r="14" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="54" t="s">
         <v>311</v>
       </c>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="51"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
+      <c r="F14" s="56"/>
     </row>
     <row r="15" spans="1:6" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="35" t="s">
@@ -2776,14 +2890,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="22.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="53" t="s">
+      <c r="A17" s="58" t="s">
         <v>318</v>
       </c>
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
-      <c r="D17" s="50"/>
-      <c r="E17" s="50"/>
-      <c r="F17" s="50"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
     </row>
     <row r="18" spans="1:6" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="35" t="s">
@@ -2826,14 +2940,14 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="52" t="s">
+      <c r="A20" s="57" t="s">
         <v>325</v>
       </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="51"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="56"/>
     </row>
     <row r="21" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="35" t="s">
@@ -2876,34 +2990,34 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="52" t="s">
+      <c r="A23" s="35" t="s">
+        <v>183</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>337</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>423</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="E23" s="35">
+        <v>1</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="67" t="s">
         <v>332</v>
       </c>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="51"/>
-    </row>
-    <row r="24" spans="1:6" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="B24" s="35" t="s">
-        <v>337</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>333</v>
-      </c>
-      <c r="D24" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="E24" s="35">
-        <v>1</v>
-      </c>
-      <c r="F24" s="34" t="s">
-        <v>334</v>
-      </c>
+      <c r="B24" s="68"/>
+      <c r="C24" s="68"/>
+      <c r="D24" s="68"/>
+      <c r="E24" s="68"/>
+      <c r="F24" s="69"/>
     </row>
     <row r="25" spans="1:6" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="35" t="s">
@@ -2913,7 +3027,7 @@
         <v>400</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D25" s="35" t="s">
         <v>287</v>
@@ -2921,19 +3035,19 @@
       <c r="E25" s="35">
         <v>1</v>
       </c>
-      <c r="F25" s="37" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F25" s="34" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35" t="s">
         <v>201</v>
       </c>
       <c r="B26" s="35" t="s">
         <v>401</v>
       </c>
-      <c r="C26" s="36" t="s">
-        <v>338</v>
+      <c r="C26" s="35" t="s">
+        <v>335</v>
       </c>
       <c r="D26" s="35" t="s">
         <v>287</v>
@@ -2942,16 +3056,56 @@
         <v>1</v>
       </c>
       <c r="F26" s="37" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="35" t="s">
+        <v>413</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="C27" s="36" t="s">
+        <v>338</v>
+      </c>
+      <c r="D27" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="E27" s="35">
+        <v>1</v>
+      </c>
+      <c r="F27" s="37" t="s">
         <v>328</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="35" t="s">
+        <v>421</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>422</v>
+      </c>
+      <c r="C28" s="36" t="s">
+        <v>415</v>
+      </c>
+      <c r="D28" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="E28" s="35">
+        <v>1</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>416</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A23:F23"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A20:F20"/>
@@ -2963,7 +3117,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M46"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3058,21 +3212,21 @@
       <c r="M2" s="42"/>
     </row>
     <row r="3" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="47" t="s">
+      <c r="A3" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
     </row>
     <row r="4" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="43" t="s">
@@ -3207,21 +3361,21 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="56"/>
-      <c r="C8" s="56"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="56"/>
-      <c r="G8" s="56"/>
-      <c r="H8" s="56"/>
-      <c r="I8" s="56"/>
-      <c r="J8" s="56"/>
-      <c r="K8" s="56"/>
-      <c r="L8" s="56"/>
-      <c r="M8" s="56"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="51"/>
+      <c r="D8" s="51"/>
+      <c r="E8" s="51"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
+      <c r="I8" s="51"/>
+      <c r="J8" s="51"/>
+      <c r="K8" s="51"/>
+      <c r="L8" s="51"/>
+      <c r="M8" s="51"/>
     </row>
     <row r="9" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="43" t="s">
@@ -3323,21 +3477,21 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="56"/>
-      <c r="J12" s="56"/>
-      <c r="K12" s="56"/>
-      <c r="L12" s="56"/>
-      <c r="M12" s="56"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
     </row>
     <row r="13" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="43" t="s">
@@ -3355,7 +3509,7 @@
       <c r="E13" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="F13" s="58">
+      <c r="F13" s="48">
         <v>15000</v>
       </c>
       <c r="G13" s="45" t="s">
@@ -3434,26 +3588,26 @@
       <c r="L15" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M15" s="59" t="s">
+      <c r="M15" s="49" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="50" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="56"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="56"/>
-      <c r="L16" s="56"/>
-      <c r="M16" s="56"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="51"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
+      <c r="I16" s="51"/>
+      <c r="J16" s="51"/>
+      <c r="K16" s="51"/>
+      <c r="L16" s="51"/>
+      <c r="M16" s="51"/>
     </row>
     <row r="17" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="43" t="s">
@@ -3484,7 +3638,7 @@
       <c r="L17" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M17" s="59" t="s">
+      <c r="M17" s="49" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3517,7 +3671,7 @@
       <c r="L18" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="M18" s="59" t="s">
+      <c r="M18" s="49" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3550,7 +3704,7 @@
       <c r="L19" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M19" s="59" t="s">
+      <c r="M19" s="49" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3583,29 +3737,29 @@
       <c r="L20" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M20" s="59" t="s">
+      <c r="M20" s="49" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="B21" s="56"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="56"/>
-      <c r="J21" s="56"/>
-      <c r="K21" s="56"/>
-      <c r="L21" s="56"/>
-      <c r="M21" s="56"/>
+      <c r="B21" s="51"/>
+      <c r="C21" s="51"/>
+      <c r="D21" s="51"/>
+      <c r="E21" s="51"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="51"/>
     </row>
     <row r="22" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="47" t="s">
         <v>103</v>
       </c>
       <c r="B22" s="44" t="s">
@@ -3633,12 +3787,12 @@
       <c r="L22" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M22" s="59" t="s">
+      <c r="M22" s="49" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="57" t="s">
+      <c r="A23" s="47" t="s">
         <v>109</v>
       </c>
       <c r="B23" s="44" t="s">
@@ -3666,12 +3820,12 @@
       <c r="L23" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M23" s="59" t="s">
+      <c r="M23" s="49" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="57" t="s">
+      <c r="A24" s="47" t="s">
         <v>115</v>
       </c>
       <c r="B24" s="44" t="s">
@@ -3699,12 +3853,12 @@
       <c r="L24" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M24" s="59" t="s">
+      <c r="M24" s="49" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="57" t="s">
+      <c r="A25" s="47" t="s">
         <v>123</v>
       </c>
       <c r="B25" s="44" t="s">
@@ -3732,29 +3886,29 @@
       <c r="L25" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M25" s="59" t="s">
+      <c r="M25" s="49" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="55" t="s">
+      <c r="A26" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="56"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="56"/>
-      <c r="J26" s="56"/>
-      <c r="K26" s="56"/>
-      <c r="L26" s="56"/>
-      <c r="M26" s="56"/>
+      <c r="B26" s="51"/>
+      <c r="C26" s="51"/>
+      <c r="D26" s="51"/>
+      <c r="E26" s="51"/>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="51"/>
+      <c r="K26" s="51"/>
+      <c r="L26" s="51"/>
+      <c r="M26" s="51"/>
     </row>
     <row r="27" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="57" t="s">
+      <c r="A27" s="47" t="s">
         <v>128</v>
       </c>
       <c r="B27" s="44" t="s">
@@ -3782,12 +3936,12 @@
       <c r="L27" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M27" s="59" t="s">
+      <c r="M27" s="49" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="57" t="s">
+      <c r="A28" s="47" t="s">
         <v>134</v>
       </c>
       <c r="B28" s="44" t="s">
@@ -3815,12 +3969,12 @@
       <c r="L28" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="M28" s="59" t="s">
+      <c r="M28" s="49" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="57" t="s">
+      <c r="A29" s="47" t="s">
         <v>139</v>
       </c>
       <c r="B29" s="44" t="s">
@@ -3848,12 +4002,12 @@
       <c r="L29" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M29" s="59" t="s">
+      <c r="M29" s="49" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="57" t="s">
+      <c r="A30" s="47" t="s">
         <v>141</v>
       </c>
       <c r="B30" s="44" t="s">
@@ -3881,12 +4035,12 @@
       <c r="L30" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M30" s="59" t="s">
+      <c r="M30" s="49" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="47" t="s">
         <v>148</v>
       </c>
       <c r="B31" s="44" t="s">
@@ -3914,12 +4068,12 @@
       <c r="L31" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M31" s="59" t="s">
+      <c r="M31" s="49" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="57" t="s">
+      <c r="A32" s="47" t="s">
         <v>153</v>
       </c>
       <c r="B32" s="44" t="s">
@@ -3947,29 +4101,29 @@
       <c r="L32" s="43" t="s">
         <v>41</v>
       </c>
-      <c r="M32" s="59" t="s">
+      <c r="M32" s="49" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="55" t="s">
+      <c r="A33" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
-      <c r="G33" s="56"/>
-      <c r="H33" s="56"/>
-      <c r="I33" s="56"/>
-      <c r="J33" s="56"/>
-      <c r="K33" s="56"/>
-      <c r="L33" s="56"/>
-      <c r="M33" s="56"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="51"/>
+      <c r="D33" s="51"/>
+      <c r="E33" s="51"/>
+      <c r="F33" s="51"/>
+      <c r="G33" s="51"/>
+      <c r="H33" s="51"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="51"/>
+      <c r="K33" s="51"/>
+      <c r="L33" s="51"/>
+      <c r="M33" s="51"/>
     </row>
     <row r="34" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="57" t="s">
+      <c r="A34" s="47" t="s">
         <v>159</v>
       </c>
       <c r="B34" s="44" t="s">
@@ -3997,12 +4151,12 @@
       <c r="L34" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M34" s="59" t="s">
+      <c r="M34" s="49" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="57" t="s">
+      <c r="A35" s="47" t="s">
         <v>164</v>
       </c>
       <c r="B35" s="44" t="s">
@@ -4030,12 +4184,12 @@
       <c r="L35" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M35" s="59" t="s">
+      <c r="M35" s="49" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="36" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="57" t="s">
+      <c r="A36" s="47" t="s">
         <v>170</v>
       </c>
       <c r="B36" s="44" t="s">
@@ -4063,12 +4217,12 @@
       <c r="L36" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M36" s="59" t="s">
+      <c r="M36" s="49" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="57" t="s">
+      <c r="A37" s="47" t="s">
         <v>176</v>
       </c>
       <c r="B37" s="44" t="s">
@@ -4096,29 +4250,29 @@
       <c r="L37" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M37" s="59" t="s">
+      <c r="M37" s="49" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="55" t="s">
+      <c r="A38" s="50" t="s">
         <v>205</v>
       </c>
-      <c r="B38" s="56"/>
-      <c r="C38" s="56"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="56"/>
-      <c r="I38" s="56"/>
-      <c r="J38" s="56"/>
-      <c r="K38" s="56"/>
-      <c r="L38" s="56"/>
-      <c r="M38" s="56"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="51"/>
+      <c r="F38" s="51"/>
+      <c r="G38" s="51"/>
+      <c r="H38" s="51"/>
+      <c r="I38" s="51"/>
+      <c r="J38" s="51"/>
+      <c r="K38" s="51"/>
+      <c r="L38" s="51"/>
+      <c r="M38" s="51"/>
     </row>
     <row r="39" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="57" t="s">
+      <c r="A39" s="47" t="s">
         <v>184</v>
       </c>
       <c r="B39" s="44" t="s">
@@ -4133,10 +4287,10 @@
       <c r="E39" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="F39" s="44" t="s">
+      <c r="F39" s="63" t="s">
         <v>210</v>
       </c>
-      <c r="G39" s="45" t="s">
+      <c r="G39" s="49" t="s">
         <v>211</v>
       </c>
       <c r="H39" s="44"/>
@@ -4151,7 +4305,7 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="57" t="s">
+      <c r="A40" s="47" t="s">
         <v>189</v>
       </c>
       <c r="B40" s="44" t="s">
@@ -4183,77 +4337,75 @@
         <v>169</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="55" t="s">
+    <row r="41" spans="1:13" ht="76.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="60" t="s">
+        <v>195</v>
+      </c>
+      <c r="B41" s="61" t="s">
+        <v>417</v>
+      </c>
+      <c r="C41" s="62" t="s">
+        <v>207</v>
+      </c>
+      <c r="D41" s="61" t="s">
+        <v>418</v>
+      </c>
+      <c r="E41" s="70" t="s">
+        <v>419</v>
+      </c>
+      <c r="F41" s="64" t="s">
+        <v>210</v>
+      </c>
+      <c r="G41" s="65" t="s">
+        <v>420</v>
+      </c>
+      <c r="I41" s="66"/>
+      <c r="K41" s="66"/>
+      <c r="L41" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="M41" s="72" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="81" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="50" t="s">
         <v>216</v>
       </c>
-      <c r="B41" s="56"/>
-      <c r="C41" s="56"/>
-      <c r="D41" s="56"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="56"/>
-      <c r="I41" s="56"/>
-      <c r="J41" s="56"/>
-      <c r="K41" s="56"/>
-      <c r="L41" s="56"/>
-      <c r="M41" s="56"/>
-    </row>
-    <row r="42" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="57" t="s">
-        <v>195</v>
-      </c>
-      <c r="B42" s="44" t="s">
-        <v>217</v>
-      </c>
-      <c r="C42" s="45" t="s">
-        <v>406</v>
-      </c>
-      <c r="D42" s="44" t="s">
-        <v>407</v>
-      </c>
-      <c r="E42" s="45" t="s">
-        <v>218</v>
-      </c>
-      <c r="F42" s="44" t="s">
-        <v>219</v>
-      </c>
-      <c r="G42" s="45" t="s">
-        <v>220</v>
-      </c>
-      <c r="H42" s="44"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="44"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="M42" s="59" t="s">
-        <v>183</v>
-      </c>
+      <c r="B42" s="51"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+      <c r="J42" s="51"/>
+      <c r="K42" s="51"/>
+      <c r="L42" s="51"/>
+      <c r="M42" s="51"/>
     </row>
     <row r="43" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="57" t="s">
+      <c r="A43" s="47" t="s">
         <v>200</v>
       </c>
       <c r="B43" s="44" t="s">
         <v>217</v>
       </c>
       <c r="C43" s="45" t="s">
-        <v>221</v>
+        <v>406</v>
       </c>
       <c r="D43" s="44" t="s">
-        <v>222</v>
+        <v>407</v>
       </c>
       <c r="E43" s="45" t="s">
-        <v>408</v>
+        <v>218</v>
       </c>
       <c r="F43" s="44" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G43" s="45" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="H43" s="44"/>
       <c r="I43" s="45"/>
@@ -4262,31 +4414,31 @@
       <c r="L43" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M43" s="59" t="s">
-        <v>183</v>
+      <c r="M43" s="49" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="57" t="s">
+      <c r="A44" s="47" t="s">
         <v>202</v>
       </c>
       <c r="B44" s="44" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="C44" s="45" t="s">
-        <v>409</v>
+        <v>221</v>
       </c>
       <c r="D44" s="44" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E44" s="45" t="s">
-        <v>227</v>
+        <v>408</v>
       </c>
       <c r="F44" s="44" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G44" s="45" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="H44" s="44"/>
       <c r="I44" s="45"/>
@@ -4295,13 +4447,79 @@
       <c r="L44" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="M44" s="59" t="s">
+      <c r="M44" s="49" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="47" t="s">
+        <v>202</v>
+      </c>
+      <c r="B45" s="44" t="s">
+        <v>225</v>
+      </c>
+      <c r="C45" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="D45" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="E45" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="F45" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="G45" s="45" t="s">
+        <v>229</v>
+      </c>
+      <c r="H45" s="44"/>
+      <c r="I45" s="45"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="45"/>
+      <c r="L45" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="M45" s="49" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="48" x14ac:dyDescent="0.3">
+      <c r="A46" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="B46" s="44" t="s">
+        <v>410</v>
+      </c>
+      <c r="C46" s="45" t="s">
+        <v>409</v>
+      </c>
+      <c r="D46" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="E46" s="45" t="s">
+        <v>411</v>
+      </c>
+      <c r="F46" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="G46" s="45" t="s">
+        <v>412</v>
+      </c>
+      <c r="H46" s="44"/>
+      <c r="I46" s="45"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="45"/>
+      <c r="L46" s="46" t="s">
+        <v>29</v>
+      </c>
+      <c r="M46" s="49" t="s">
+        <v>413</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A41:M41"/>
+    <mergeCell ref="A42:M42"/>
     <mergeCell ref="A3:M3"/>
     <mergeCell ref="A26:M26"/>
     <mergeCell ref="A33:M33"/>
@@ -4963,17 +5181,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="59" t="s">
         <v>384</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
     </row>
     <row r="2" spans="1:9" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
